--- a/ФИО и должности сварищики.xlsx
+++ b/ФИО и должности сварищики.xlsx
@@ -11,7 +11,7 @@
     <sheet r:id="rId2" sheetId="2" name="Сварочные должности"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">='Все уникальные'!$A$1:$B$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">='Все уникальные'!$A$1:$B$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Сварочные должности'!$A$1:$B$117</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="122">
   <si>
     <t>ФИО</t>
   </si>
@@ -761,7 +761,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="3" width="42.71928571428572" customWidth="1" bestFit="1"/>
@@ -1330,7 +1330,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>5</v>
@@ -1338,15 +1338,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>62</v>
@@ -1354,31 +1354,31 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>3</v>
@@ -1386,15 +1386,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>5</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>5</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>5</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>5</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>5</v>
@@ -1434,7 +1434,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>5</v>
@@ -1442,7 +1442,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>5</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>5</v>
@@ -1458,23 +1458,23 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>3</v>
@@ -1482,31 +1482,31 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>5</v>
@@ -1514,47 +1514,47 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>5</v>
@@ -1562,15 +1562,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>5</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>5</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>5</v>
@@ -1594,25 +1594,9 @@
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
-      <c r="A105" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
-      <c r="A106" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B106" s="2" t="s">
         <v>121</v>
       </c>
     </row>
